--- a/marketer_forms/005_t_shirt_survey--marketer_forms.xlsx
+++ b/marketer_forms/005_t_shirt_survey--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'13-16'}</t>
+          <t>13-16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '13-16'}</t>
+          <t>13-16</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'17-24'}</t>
+          <t>17-24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '17-24'}</t>
+          <t>17-24</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'55_or_older'}</t>
+          <t>55_or_older</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': '55 or older'}</t>
+          <t>55 or older</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'xl'}</t>
+          <t>xl</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'XL'}</t>
+          <t>XL</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'graphic'}</t>
+          <t>graphic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Graphic'}</t>
+          <t>Graphic</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'text'}</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Text'}</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'logo'}</t>
+          <t>logo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Logo'}</t>
+          <t>Logo</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'xl'}</t>
+          <t>xl</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'XL'}</t>
+          <t>XL</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'short'}</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Short'}</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'long'}</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Long'}</t>
+          <t>Long</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'extra_long'}</t>
+          <t>extra_long</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Extra Long'}</t>
+          <t>Extra Long</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'casual'}</t>
+          <t>casual</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Casual'}</t>
+          <t>Casual</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'formal'}</t>
+          <t>formal</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Formal'}</t>
+          <t>Formal</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'short'}</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Short'}</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'long'}</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Long'}</t>
+          <t>Long</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'short'}</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Short'}</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'long'}</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Long'}</t>
+          <t>Long</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'extra_long'}</t>
+          <t>extra_long</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Extra Long'}</t>
+          <t>Extra Long</t>
         </is>
       </c>
     </row>
